--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128337994</v>
+        <v>128338213</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574735</v>
+        <v>574711</v>
       </c>
       <c r="R3" t="n">
-        <v>7088435</v>
+        <v>7088512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338213</v>
+        <v>128338613</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574711</v>
+        <v>574703</v>
       </c>
       <c r="R4" t="n">
-        <v>7088512</v>
+        <v>7088527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338143</v>
+        <v>128338659</v>
       </c>
       <c r="B17" t="n">
         <v>57672</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574745</v>
+        <v>574695</v>
       </c>
       <c r="R17" t="n">
-        <v>7088485</v>
+        <v>7088514</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,14 +2438,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,19 +2470,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343178</v>
+        <v>128338143</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2512,13 +2522,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574894</v>
+        <v>574745</v>
       </c>
       <c r="R18" t="n">
-        <v>7088378</v>
+        <v>7088485</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,24 +2555,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,19 +2577,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128338659</v>
+        <v>128343178</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574695</v>
+        <v>574894</v>
       </c>
       <c r="R19" t="n">
-        <v>7088514</v>
+        <v>7088378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B3" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R3" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>78789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R4" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128338768</v>
+        <v>128338633</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574690</v>
+        <v>574688</v>
       </c>
       <c r="R6" t="n">
-        <v>7088519</v>
+        <v>7088504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128343166</v>
+        <v>128338768</v>
       </c>
       <c r="B7" t="n">
         <v>57672</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574867</v>
+        <v>574690</v>
       </c>
       <c r="R7" t="n">
-        <v>7088386</v>
+        <v>7088519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128338633</v>
+        <v>128343166</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574688</v>
+        <v>574867</v>
       </c>
       <c r="R8" t="n">
-        <v>7088504</v>
+        <v>7088386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338557</v>
+        <v>128338797</v>
       </c>
       <c r="B26" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,37 +3379,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574714</v>
+        <v>574687</v>
       </c>
       <c r="R26" t="n">
-        <v>7088538</v>
+        <v>7088513</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,9 +3441,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,19 +3473,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338797</v>
+        <v>128338722</v>
       </c>
       <c r="B27" t="n">
         <v>57672</v>
@@ -3505,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574687</v>
+        <v>574686</v>
       </c>
       <c r="R27" t="n">
-        <v>7088513</v>
+        <v>7088504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3550,7 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3582,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,42 +3613,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R28" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,24 +3670,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338040</v>
+        <v>128338482</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>92681</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,42 +5639,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574732</v>
+        <v>574715</v>
       </c>
       <c r="R46" t="n">
-        <v>7088443</v>
+        <v>7088499</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5701,24 +5696,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5733,22 +5713,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338482</v>
+        <v>128338040</v>
       </c>
       <c r="B47" t="n">
-        <v>92681</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5756,37 +5736,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574715</v>
+        <v>574732</v>
       </c>
       <c r="R47" t="n">
-        <v>7088499</v>
+        <v>7088443</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5813,9 +5798,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,12 +5830,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338659</v>
+        <v>128338143</v>
       </c>
       <c r="B17" t="n">
         <v>57672</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574695</v>
+        <v>574745</v>
       </c>
       <c r="R17" t="n">
-        <v>7088514</v>
+        <v>7088485</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,24 +2438,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,19 +2460,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128338143</v>
+        <v>128343178</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2522,13 +2512,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574745</v>
+        <v>574894</v>
       </c>
       <c r="R18" t="n">
-        <v>7088485</v>
+        <v>7088378</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,14 +2545,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,19 +2577,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343178</v>
+        <v>128338659</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574894</v>
+        <v>574695</v>
       </c>
       <c r="R19" t="n">
-        <v>7088378</v>
+        <v>7088514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4391,7 +4391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128338455</v>
+        <v>128343586</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574714</v>
+        <v>574972</v>
       </c>
       <c r="R35" t="n">
-        <v>7088466</v>
+        <v>7088368</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R36" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343586</v>
+        <v>128338455</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574972</v>
+        <v>574714</v>
       </c>
       <c r="R37" t="n">
-        <v>7088368</v>
+        <v>7088466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4742,7 +4742,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R38" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128343377</v>
+        <v>128338638</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,39 +6281,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574939</v>
+        <v>574703</v>
       </c>
       <c r="R52" t="n">
-        <v>7088378</v>
+        <v>7088547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,12 +6350,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,22 +6365,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338638</v>
+        <v>128338816</v>
       </c>
       <c r="B53" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6398,34 +6388,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574703</v>
+        <v>574676</v>
       </c>
       <c r="R53" t="n">
-        <v>7088547</v>
+        <v>7088536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6467,7 +6462,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,19 +6482,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338816</v>
+        <v>128343377</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574676</v>
+        <v>574939</v>
       </c>
       <c r="R54" t="n">
-        <v>7088536</v>
+        <v>7088378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128337994</v>
+        <v>128338213</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574735</v>
+        <v>574711</v>
       </c>
       <c r="R3" t="n">
-        <v>7088435</v>
+        <v>7088512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338213</v>
+        <v>128338613</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574711</v>
+        <v>574703</v>
       </c>
       <c r="R4" t="n">
-        <v>7088512</v>
+        <v>7088527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128338633</v>
+        <v>128338768</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574688</v>
+        <v>574690</v>
       </c>
       <c r="R6" t="n">
-        <v>7088504</v>
+        <v>7088519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128338768</v>
+        <v>128343166</v>
       </c>
       <c r="B7" t="n">
         <v>57672</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574690</v>
+        <v>574867</v>
       </c>
       <c r="R7" t="n">
-        <v>7088519</v>
+        <v>7088386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128343166</v>
+        <v>128338633</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574867</v>
+        <v>574688</v>
       </c>
       <c r="R8" t="n">
-        <v>7088386</v>
+        <v>7088504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128343586</v>
+        <v>128338455</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574972</v>
+        <v>574714</v>
       </c>
       <c r="R35" t="n">
-        <v>7088368</v>
+        <v>7088466</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R36" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128338455</v>
+        <v>128343586</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574714</v>
+        <v>574972</v>
       </c>
       <c r="R37" t="n">
-        <v>7088466</v>
+        <v>7088368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4742,7 +4742,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R38" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B52" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,34 +6281,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R52" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6345,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,7 +6355,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,22 +6375,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6388,39 +6398,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R53" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6452,7 +6457,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,12 +6467,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,19 +6482,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R54" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128338768</v>
+        <v>128338633</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574690</v>
+        <v>574688</v>
       </c>
       <c r="R6" t="n">
-        <v>7088519</v>
+        <v>7088504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128343166</v>
+        <v>128338768</v>
       </c>
       <c r="B7" t="n">
         <v>57672</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574867</v>
+        <v>574690</v>
       </c>
       <c r="R7" t="n">
-        <v>7088386</v>
+        <v>7088519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128338633</v>
+        <v>128343166</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574688</v>
+        <v>574867</v>
       </c>
       <c r="R8" t="n">
-        <v>7088504</v>
+        <v>7088386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338599</v>
+        <v>128338416</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>78790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574696</v>
+        <v>574700</v>
       </c>
       <c r="R11" t="n">
-        <v>7088527</v>
+        <v>7088515</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,19 +1771,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1788,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338117</v>
+        <v>128338599</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574773</v>
+        <v>574696</v>
       </c>
       <c r="R12" t="n">
-        <v>7088446</v>
+        <v>7088527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338416</v>
+        <v>128338117</v>
       </c>
       <c r="B13" t="n">
-        <v>78790</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,37 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574700</v>
+        <v>574773</v>
       </c>
       <c r="R13" t="n">
-        <v>7088515</v>
+        <v>7088446</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,9 +1980,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128343150</v>
+        <v>128343435</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3730,7 +3730,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574851</v>
+        <v>574990</v>
       </c>
       <c r="R29" t="n">
-        <v>7088391</v>
+        <v>7088393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3816,7 +3816,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128343147</v>
+        <v>128343150</v>
       </c>
       <c r="B30" t="n">
         <v>57672</v>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574870</v>
+        <v>574851</v>
       </c>
       <c r="R30" t="n">
-        <v>7088372</v>
+        <v>7088391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3921,19 +3921,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128343435</v>
+        <v>128343147</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3964,7 +3964,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574990</v>
+        <v>574870</v>
       </c>
       <c r="R31" t="n">
-        <v>7088393</v>
+        <v>7088372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4038,12 +4038,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128338455</v>
+        <v>128343586</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574714</v>
+        <v>574972</v>
       </c>
       <c r="R35" t="n">
-        <v>7088466</v>
+        <v>7088368</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R36" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343586</v>
+        <v>128338455</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574972</v>
+        <v>574714</v>
       </c>
       <c r="R37" t="n">
-        <v>7088368</v>
+        <v>7088466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4742,7 +4742,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R38" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128343377</v>
+        <v>128338638</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,39 +6281,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574939</v>
+        <v>574703</v>
       </c>
       <c r="R52" t="n">
-        <v>7088378</v>
+        <v>7088547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,12 +6350,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,22 +6365,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338638</v>
+        <v>128338816</v>
       </c>
       <c r="B53" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6398,34 +6388,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574703</v>
+        <v>574676</v>
       </c>
       <c r="R53" t="n">
-        <v>7088547</v>
+        <v>7088536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6467,7 +6462,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,19 +6482,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338816</v>
+        <v>128343377</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574676</v>
+        <v>574939</v>
       </c>
       <c r="R54" t="n">
-        <v>7088536</v>
+        <v>7088378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B3" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R3" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>78789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R4" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338416</v>
+        <v>128338599</v>
       </c>
       <c r="B11" t="n">
-        <v>78790</v>
+        <v>79031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574700</v>
+        <v>574696</v>
       </c>
       <c r="R11" t="n">
-        <v>7088515</v>
+        <v>7088527</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,9 +1771,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338599</v>
+        <v>128338117</v>
       </c>
       <c r="B12" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574696</v>
+        <v>574773</v>
       </c>
       <c r="R12" t="n">
-        <v>7088527</v>
+        <v>7088446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338117</v>
+        <v>128338416</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1938,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574773</v>
+        <v>574700</v>
       </c>
       <c r="R13" t="n">
-        <v>7088446</v>
+        <v>7088515</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,24 +1995,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338143</v>
+        <v>128338659</v>
       </c>
       <c r="B17" t="n">
         <v>57672</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574745</v>
+        <v>574695</v>
       </c>
       <c r="R17" t="n">
-        <v>7088485</v>
+        <v>7088514</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,14 +2438,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,19 +2470,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128343178</v>
+        <v>128338143</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2512,13 +2522,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574894</v>
+        <v>574745</v>
       </c>
       <c r="R18" t="n">
-        <v>7088378</v>
+        <v>7088485</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,24 +2555,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,19 +2577,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128338659</v>
+        <v>128343178</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574695</v>
+        <v>574894</v>
       </c>
       <c r="R19" t="n">
-        <v>7088514</v>
+        <v>7088378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338797</v>
+        <v>128338557</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,42 +3379,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574687</v>
+        <v>574714</v>
       </c>
       <c r="R26" t="n">
-        <v>7088513</v>
+        <v>7088538</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,24 +3436,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,19 +3453,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338722</v>
+        <v>128338797</v>
       </c>
       <c r="B27" t="n">
         <v>57672</v>
@@ -3525,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574686</v>
+        <v>574687</v>
       </c>
       <c r="R27" t="n">
-        <v>7088504</v>
+        <v>7088513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3602,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338557</v>
+        <v>128338722</v>
       </c>
       <c r="B28" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,37 +3593,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574714</v>
+        <v>574686</v>
       </c>
       <c r="R28" t="n">
-        <v>7088538</v>
+        <v>7088504</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,9 +3655,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338474</v>
+        <v>128338121</v>
       </c>
       <c r="B32" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,34 +4061,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574723</v>
+        <v>574730</v>
       </c>
       <c r="R32" t="n">
-        <v>7088471</v>
+        <v>7088455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4135,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,7 +4167,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338121</v>
+        <v>128338569</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4197,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574730</v>
+        <v>574741</v>
       </c>
       <c r="R33" t="n">
-        <v>7088455</v>
+        <v>7088549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,12 +4252,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338569</v>
+        <v>128338474</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,39 +4295,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574741</v>
+        <v>574723</v>
       </c>
       <c r="R34" t="n">
-        <v>7088549</v>
+        <v>7088471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4379,19 +4379,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128343586</v>
+        <v>128338455</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574972</v>
+        <v>574714</v>
       </c>
       <c r="R35" t="n">
-        <v>7088368</v>
+        <v>7088466</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R36" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4625,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128338455</v>
+        <v>128343586</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574714</v>
+        <v>574972</v>
       </c>
       <c r="R37" t="n">
-        <v>7088466</v>
+        <v>7088368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4742,7 +4742,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R38" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B52" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,34 +6281,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R52" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6345,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,7 +6355,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,22 +6375,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6388,39 +6398,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R53" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6452,7 +6457,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,12 +6467,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,19 +6482,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B54" t="n">
         <v>57672</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R54" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128343651</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R3" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R4" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>78790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R5" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>128338633</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128338768</v>
+        <v>128343166</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574690</v>
+        <v>574867</v>
       </c>
       <c r="R7" t="n">
-        <v>7088519</v>
+        <v>7088386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128343166</v>
+        <v>128338768</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574867</v>
+        <v>574690</v>
       </c>
       <c r="R8" t="n">
-        <v>7088386</v>
+        <v>7088519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         <v>128344576</v>
       </c>
       <c r="B9" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>128343338</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338599</v>
+        <v>128338416</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574696</v>
+        <v>574700</v>
       </c>
       <c r="R11" t="n">
-        <v>7088527</v>
+        <v>7088515</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,19 +1771,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1788,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338117</v>
+        <v>128338599</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574773</v>
+        <v>574696</v>
       </c>
       <c r="R12" t="n">
-        <v>7088446</v>
+        <v>7088527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338416</v>
+        <v>128338117</v>
       </c>
       <c r="B13" t="n">
-        <v>78790</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,37 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574700</v>
+        <v>574773</v>
       </c>
       <c r="R13" t="n">
-        <v>7088515</v>
+        <v>7088446</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,9 +1980,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
         <v>128338304</v>
       </c>
       <c r="B14" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R15" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343288</v>
+        <v>128343440</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574931</v>
+        <v>574954</v>
       </c>
       <c r="R16" t="n">
-        <v>7088374</v>
+        <v>7088370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2368,7 +2368,7 @@
         <v>128338659</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128338143</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128343178</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>82872</v>
+        <v>82873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>128343500</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>128343223</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B23" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,34 +3058,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R23" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3132,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,22 +3152,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,39 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R24" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,12 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>128338166</v>
       </c>
       <c r="B25" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338557</v>
+        <v>128338722</v>
       </c>
       <c r="B26" t="n">
-        <v>78789</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,37 +3379,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574714</v>
+        <v>574686</v>
       </c>
       <c r="R26" t="n">
-        <v>7088538</v>
+        <v>7088504</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,9 +3441,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,12 +3473,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3468,7 +3488,7 @@
         <v>128338797</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3582,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,42 +3613,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R28" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,24 +3670,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,22 +3687,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128343435</v>
+        <v>128343150</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574990</v>
+        <v>574851</v>
       </c>
       <c r="R29" t="n">
-        <v>7088393</v>
+        <v>7088391</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128343150</v>
+        <v>128343435</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574851</v>
+        <v>574990</v>
       </c>
       <c r="R30" t="n">
-        <v>7088391</v>
+        <v>7088393</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3936,7 +3936,7 @@
         <v>128343147</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338121</v>
+        <v>128338474</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>79650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,39 +4061,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574730</v>
+        <v>574723</v>
       </c>
       <c r="R32" t="n">
-        <v>7088455</v>
+        <v>7088471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4125,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,12 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4170,7 +4160,7 @@
         <v>128338569</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338474</v>
+        <v>128338121</v>
       </c>
       <c r="B34" t="n">
-        <v>79649</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4295,34 +4285,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574723</v>
+        <v>574730</v>
       </c>
       <c r="R34" t="n">
-        <v>7088471</v>
+        <v>7088455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4354,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128338455</v>
+        <v>128338540</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574714</v>
+        <v>574700</v>
       </c>
       <c r="R35" t="n">
-        <v>7088466</v>
+        <v>7088489</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128338540</v>
+        <v>128338455</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574700</v>
+        <v>574714</v>
       </c>
       <c r="R36" t="n">
-        <v>7088489</v>
+        <v>7088466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343586</v>
+        <v>128343702</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574972</v>
+        <v>575023</v>
       </c>
       <c r="R37" t="n">
-        <v>7088368</v>
+        <v>7088330</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4742,10 +4742,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128343702</v>
+        <v>128343586</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575023</v>
+        <v>574972</v>
       </c>
       <c r="R38" t="n">
-        <v>7088330</v>
+        <v>7088368</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4862,7 +4862,7 @@
         <v>128338494</v>
       </c>
       <c r="B39" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338573</v>
+        <v>128338168</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,39 +4977,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574708</v>
+        <v>574729</v>
       </c>
       <c r="R40" t="n">
-        <v>7088494</v>
+        <v>7088442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,12 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,7 +5076,7 @@
         <v>128338072</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5200,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128338168</v>
+        <v>128343543</v>
       </c>
       <c r="B42" t="n">
-        <v>79649</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5211,34 +5201,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574729</v>
+        <v>574962</v>
       </c>
       <c r="R42" t="n">
-        <v>7088442</v>
+        <v>7088368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5270,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5280,7 +5275,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128343543</v>
+        <v>128338573</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574962</v>
+        <v>574708</v>
       </c>
       <c r="R43" t="n">
-        <v>7088368</v>
+        <v>7088494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91616</v>
+        <v>91621</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338412</v>
+        <v>128338615</v>
       </c>
       <c r="B45" t="n">
-        <v>78789</v>
+        <v>92843</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574702</v>
+        <v>574720</v>
       </c>
       <c r="R45" t="n">
-        <v>7088517</v>
+        <v>7088539</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,12 +5606,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5631,7 +5621,7 @@
         <v>128338482</v>
       </c>
       <c r="B46" t="n">
-        <v>92681</v>
+        <v>92686</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,10 +5715,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338040</v>
+        <v>128338412</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,39 +5726,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574732</v>
+        <v>574702</v>
       </c>
       <c r="R47" t="n">
-        <v>7088443</v>
+        <v>7088517</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,7 +5785,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5810,12 +5795,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5810,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338615</v>
+        <v>128338040</v>
       </c>
       <c r="B48" t="n">
-        <v>92838</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,37 +5833,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574720</v>
+        <v>574732</v>
       </c>
       <c r="R48" t="n">
-        <v>7088539</v>
+        <v>7088443</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5910,9 +5895,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
         <v>128338607</v>
       </c>
       <c r="B49" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78789</v>
+        <v>57673</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R52" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6387,10 +6387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B53" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6398,34 +6398,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R53" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,7 +6462,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6467,7 +6472,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,22 +6492,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6505,39 +6515,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R54" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,12 +6599,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338168</v>
+        <v>128338573</v>
       </c>
       <c r="B40" t="n">
-        <v>79650</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,34 +4977,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574729</v>
+        <v>574708</v>
       </c>
       <c r="R40" t="n">
-        <v>7088442</v>
+        <v>7088494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5036,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5051,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128338072</v>
+        <v>128338168</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>79650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,39 +5094,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574723</v>
+        <v>574729</v>
       </c>
       <c r="R41" t="n">
-        <v>7088461</v>
+        <v>7088442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5148,7 +5153,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5158,12 +5163,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5190,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128343543</v>
+        <v>128338072</v>
       </c>
       <c r="B42" t="n">
         <v>57673</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574962</v>
+        <v>574723</v>
       </c>
       <c r="R42" t="n">
-        <v>7088368</v>
+        <v>7088461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,7 +5307,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128338573</v>
+        <v>128343543</v>
       </c>
       <c r="B43" t="n">
         <v>57673</v>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574708</v>
+        <v>574962</v>
       </c>
       <c r="R43" t="n">
-        <v>7088494</v>
+        <v>7088368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338615</v>
+        <v>128338412</v>
       </c>
       <c r="B45" t="n">
-        <v>92843</v>
+        <v>78790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574720</v>
+        <v>574702</v>
       </c>
       <c r="R45" t="n">
-        <v>7088539</v>
+        <v>7088517</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,9 +5589,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5606,22 +5616,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338482</v>
+        <v>128338615</v>
       </c>
       <c r="B46" t="n">
-        <v>92686</v>
+        <v>92843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,21 +5639,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,10 +5663,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574715</v>
+        <v>574720</v>
       </c>
       <c r="R46" t="n">
-        <v>7088499</v>
+        <v>7088539</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5715,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338412</v>
+        <v>128338482</v>
       </c>
       <c r="B47" t="n">
-        <v>78790</v>
+        <v>92686</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5726,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5750,13 +5760,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574702</v>
+        <v>574715</v>
       </c>
       <c r="R47" t="n">
-        <v>7088517</v>
+        <v>7088499</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5783,19 +5793,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,12 +5810,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128343651</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R3" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +902,7 @@
         <v>128337994</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338213</v>
+        <v>128338613</v>
       </c>
       <c r="B5" t="n">
-        <v>78790</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574711</v>
+        <v>574703</v>
       </c>
       <c r="R5" t="n">
-        <v>7088512</v>
+        <v>7088527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128338633</v>
+        <v>128338768</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574688</v>
+        <v>574690</v>
       </c>
       <c r="R6" t="n">
-        <v>7088504</v>
+        <v>7088519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128343166</v>
+        <v>128338633</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574867</v>
+        <v>574688</v>
       </c>
       <c r="R7" t="n">
-        <v>7088386</v>
+        <v>7088504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128338768</v>
+        <v>128343166</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574690</v>
+        <v>574867</v>
       </c>
       <c r="R8" t="n">
-        <v>7088519</v>
+        <v>7088386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         <v>128344576</v>
       </c>
       <c r="B9" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>128343338</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338416</v>
+        <v>128338599</v>
       </c>
       <c r="B11" t="n">
-        <v>78791</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574700</v>
+        <v>574696</v>
       </c>
       <c r="R11" t="n">
-        <v>7088515</v>
+        <v>7088527</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,9 +1771,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338599</v>
+        <v>128338117</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574696</v>
+        <v>574773</v>
       </c>
       <c r="R12" t="n">
-        <v>7088527</v>
+        <v>7088446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338117</v>
+        <v>128338416</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1938,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574773</v>
+        <v>574700</v>
       </c>
       <c r="R13" t="n">
-        <v>7088446</v>
+        <v>7088515</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,24 +1995,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
         <v>128338304</v>
       </c>
       <c r="B14" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343288</v>
+        <v>128343440</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574931</v>
+        <v>574954</v>
       </c>
       <c r="R15" t="n">
-        <v>7088374</v>
+        <v>7088370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R16" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128338659</v>
+        <v>128343178</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574695</v>
+        <v>574894</v>
       </c>
       <c r="R17" t="n">
-        <v>7088514</v>
+        <v>7088378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128338143</v>
+        <v>128338659</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574745</v>
+        <v>574695</v>
       </c>
       <c r="R18" t="n">
-        <v>7088485</v>
+        <v>7088514</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,14 +2555,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2587,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128343178</v>
+        <v>128338143</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,13 +2639,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574894</v>
+        <v>574745</v>
       </c>
       <c r="R19" t="n">
-        <v>7088378</v>
+        <v>7088485</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,24 +2672,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,12 +2694,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>128343500</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>128343223</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,39 +3058,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R23" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,12 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,22 +3142,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,34 +3165,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R24" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3239,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,44 +3259,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338166</v>
+        <v>128338557</v>
       </c>
       <c r="B25" t="n">
-        <v>92650</v>
+        <v>78840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574741</v>
+        <v>574714</v>
       </c>
       <c r="R25" t="n">
-        <v>7088453</v>
+        <v>7088538</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3371,7 +3371,7 @@
         <v>128338722</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>128338797</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,32 +3602,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338557</v>
+        <v>128338166</v>
       </c>
       <c r="B28" t="n">
-        <v>78790</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574714</v>
+        <v>574741</v>
       </c>
       <c r="R28" t="n">
-        <v>7088538</v>
+        <v>7088453</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3702,7 +3702,7 @@
         <v>128343150</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128343435</v>
+        <v>128343147</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574990</v>
+        <v>574870</v>
       </c>
       <c r="R30" t="n">
-        <v>7088393</v>
+        <v>7088372</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3921,22 +3921,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128343147</v>
+        <v>128343435</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574870</v>
+        <v>574990</v>
       </c>
       <c r="R31" t="n">
-        <v>7088372</v>
+        <v>7088393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4038,12 +4038,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4053,7 +4053,7 @@
         <v>128338474</v>
       </c>
       <c r="B32" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>128338569</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128338121</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R35" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128338455</v>
+        <v>128338540</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574714</v>
+        <v>574700</v>
       </c>
       <c r="R36" t="n">
-        <v>7088466</v>
+        <v>7088489</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128343702</v>
+        <v>128338455</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575023</v>
+        <v>574714</v>
       </c>
       <c r="R37" t="n">
-        <v>7088330</v>
+        <v>7088466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4745,7 +4745,7 @@
         <v>128343586</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>128338494</v>
       </c>
       <c r="B39" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338573</v>
+        <v>128338168</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>79702</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,39 +4977,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574708</v>
+        <v>574729</v>
       </c>
       <c r="R40" t="n">
-        <v>7088494</v>
+        <v>7088442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,12 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128338168</v>
+        <v>128338072</v>
       </c>
       <c r="B41" t="n">
-        <v>79650</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5094,34 +5084,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574729</v>
+        <v>574723</v>
       </c>
       <c r="R41" t="n">
-        <v>7088442</v>
+        <v>7088461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5153,7 +5148,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5163,7 +5158,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5190,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128338072</v>
+        <v>128343543</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574723</v>
+        <v>574962</v>
       </c>
       <c r="R42" t="n">
-        <v>7088461</v>
+        <v>7088368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128343543</v>
+        <v>128338573</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574962</v>
+        <v>574708</v>
       </c>
       <c r="R43" t="n">
-        <v>7088368</v>
+        <v>7088494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91621</v>
+        <v>91713</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338412</v>
+        <v>128338482</v>
       </c>
       <c r="B45" t="n">
-        <v>78790</v>
+        <v>92778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574702</v>
+        <v>574715</v>
       </c>
       <c r="R45" t="n">
-        <v>7088517</v>
+        <v>7088499</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,22 +5606,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338615</v>
+        <v>128338607</v>
       </c>
       <c r="B46" t="n">
-        <v>92843</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,21 +5629,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5663,13 +5653,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574720</v>
+        <v>574695</v>
       </c>
       <c r="R46" t="n">
-        <v>7088539</v>
+        <v>7088500</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5696,9 +5686,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5713,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338482</v>
+        <v>128338615</v>
       </c>
       <c r="B47" t="n">
-        <v>92686</v>
+        <v>92935</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574715</v>
+        <v>574720</v>
       </c>
       <c r="R47" t="n">
-        <v>7088499</v>
+        <v>7088539</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338040</v>
+        <v>128338412</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>78840</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,39 +5833,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574732</v>
+        <v>574702</v>
       </c>
       <c r="R48" t="n">
-        <v>7088443</v>
+        <v>7088517</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5897,7 +5892,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5907,12 +5902,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,22 +5917,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338607</v>
+        <v>128338040</v>
       </c>
       <c r="B49" t="n">
-        <v>78791</v>
+        <v>57685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5950,34 +5940,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574695</v>
+        <v>574732</v>
       </c>
       <c r="R49" t="n">
-        <v>7088500</v>
+        <v>7088443</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6004,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6019,7 +6014,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57673</v>
+        <v>78840</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78790</v>
+        <v>57685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B52" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,39 +6281,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R52" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,12 +6350,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,22 +6365,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B53" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6427,10 +6417,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R53" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6462,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6472,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6504,10 +6494,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6515,34 +6505,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R54" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6584,7 +6579,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,12 +6599,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R4" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338482</v>
+        <v>128338615</v>
       </c>
       <c r="B45" t="n">
-        <v>92778</v>
+        <v>92935</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574715</v>
+        <v>574720</v>
       </c>
       <c r="R45" t="n">
-        <v>7088499</v>
+        <v>7088539</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338607</v>
+        <v>128338040</v>
       </c>
       <c r="B46" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,34 +5629,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574695</v>
+        <v>574732</v>
       </c>
       <c r="R46" t="n">
-        <v>7088500</v>
+        <v>7088443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5688,7 +5693,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5698,7 +5703,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5725,10 +5735,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338615</v>
+        <v>128338607</v>
       </c>
       <c r="B47" t="n">
-        <v>92935</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5746,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,13 +5770,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574720</v>
+        <v>574695</v>
       </c>
       <c r="R47" t="n">
-        <v>7088539</v>
+        <v>7088500</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5793,9 +5803,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,22 +5830,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338412</v>
+        <v>128338482</v>
       </c>
       <c r="B48" t="n">
-        <v>78840</v>
+        <v>92778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,21 +5853,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5857,13 +5877,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574702</v>
+        <v>574715</v>
       </c>
       <c r="R48" t="n">
-        <v>7088517</v>
+        <v>7088499</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5890,19 +5910,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,22 +5927,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338040</v>
+        <v>128338412</v>
       </c>
       <c r="B49" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,39 +5950,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574732</v>
+        <v>574702</v>
       </c>
       <c r="R49" t="n">
-        <v>7088443</v>
+        <v>7088517</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6004,7 +6009,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6014,12 +6019,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,22 +6034,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338117</v>
+        <v>128338416</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>78841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,42 +1821,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574773</v>
+        <v>574700</v>
       </c>
       <c r="R12" t="n">
-        <v>7088446</v>
+        <v>7088515</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,24 +1878,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338416</v>
+        <v>128338117</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,37 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574700</v>
+        <v>574773</v>
       </c>
       <c r="R13" t="n">
-        <v>7088515</v>
+        <v>7088446</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,9 +1980,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3271,32 +3271,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338557</v>
+        <v>128338166</v>
       </c>
       <c r="B25" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574714</v>
+        <v>574741</v>
       </c>
       <c r="R25" t="n">
-        <v>7088538</v>
+        <v>7088453</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,42 +3379,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R26" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,24 +3436,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,19 +3453,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338797</v>
+        <v>128338722</v>
       </c>
       <c r="B27" t="n">
         <v>57685</v>
@@ -3525,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574687</v>
+        <v>574686</v>
       </c>
       <c r="R27" t="n">
-        <v>7088513</v>
+        <v>7088504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3602,48 +3582,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338166</v>
+        <v>128338797</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574741</v>
+        <v>574687</v>
       </c>
       <c r="R28" t="n">
-        <v>7088453</v>
+        <v>7088513</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,9 +3655,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338615</v>
+        <v>128338607</v>
       </c>
       <c r="B45" t="n">
-        <v>92935</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574720</v>
+        <v>574695</v>
       </c>
       <c r="R45" t="n">
-        <v>7088539</v>
+        <v>7088500</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,9 +5589,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5606,22 +5616,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338040</v>
+        <v>128338615</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>92935</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,42 +5639,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574732</v>
+        <v>574720</v>
       </c>
       <c r="R46" t="n">
-        <v>7088443</v>
+        <v>7088539</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5691,24 +5696,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5723,22 +5713,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338607</v>
+        <v>128338482</v>
       </c>
       <c r="B47" t="n">
-        <v>78841</v>
+        <v>92778</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5746,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5770,13 +5760,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574695</v>
+        <v>574715</v>
       </c>
       <c r="R47" t="n">
-        <v>7088500</v>
+        <v>7088499</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5803,19 +5793,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5810,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338482</v>
+        <v>128338412</v>
       </c>
       <c r="B48" t="n">
-        <v>92778</v>
+        <v>78840</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,21 +5833,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5877,13 +5857,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574715</v>
+        <v>574702</v>
       </c>
       <c r="R48" t="n">
-        <v>7088499</v>
+        <v>7088517</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5910,9 +5890,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,22 +5917,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338412</v>
+        <v>128338040</v>
       </c>
       <c r="B49" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5950,34 +5940,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574702</v>
+        <v>574732</v>
       </c>
       <c r="R49" t="n">
-        <v>7088517</v>
+        <v>7088443</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6004,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6019,7 +6014,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343524</v>
+        <v>128343500</v>
       </c>
       <c r="B20" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,34 +2717,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574994</v>
+        <v>574956</v>
       </c>
       <c r="R20" t="n">
-        <v>7088388</v>
+        <v>7088362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2791,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,19 +2811,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343500</v>
+        <v>128343223</v>
       </c>
       <c r="B21" t="n">
         <v>57685</v>
@@ -2853,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574956</v>
+        <v>574927</v>
       </c>
       <c r="R21" t="n">
-        <v>7088362</v>
+        <v>7088381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2930,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343223</v>
+        <v>128343524</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>82942</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,39 +2951,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574927</v>
+        <v>574994</v>
       </c>
       <c r="R22" t="n">
-        <v>7088381</v>
+        <v>7088388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,34 +3058,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R23" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3132,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,22 +3152,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,39 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R24" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,12 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,60 +3259,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338166</v>
+        <v>128338722</v>
       </c>
       <c r="B25" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574741</v>
+        <v>574686</v>
       </c>
       <c r="R25" t="n">
-        <v>7088453</v>
+        <v>7088504</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3339,9 +3344,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,22 +3376,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338557</v>
+        <v>128338797</v>
       </c>
       <c r="B26" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,37 +3399,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574714</v>
+        <v>574687</v>
       </c>
       <c r="R26" t="n">
-        <v>7088538</v>
+        <v>7088513</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,9 +3461,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,22 +3493,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,42 +3516,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R27" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3538,24 +3573,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3570,65 +3590,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338797</v>
+        <v>128338166</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574687</v>
+        <v>574741</v>
       </c>
       <c r="R28" t="n">
-        <v>7088513</v>
+        <v>7088453</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,24 +3670,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338607</v>
+        <v>128338412</v>
       </c>
       <c r="B45" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574695</v>
+        <v>574702</v>
       </c>
       <c r="R45" t="n">
-        <v>7088500</v>
+        <v>7088517</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,22 +5616,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338615</v>
+        <v>128338040</v>
       </c>
       <c r="B46" t="n">
-        <v>92935</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,37 +5639,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574720</v>
+        <v>574732</v>
       </c>
       <c r="R46" t="n">
-        <v>7088539</v>
+        <v>7088443</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5696,9 +5701,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5733,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338482</v>
+        <v>128338607</v>
       </c>
       <c r="B47" t="n">
-        <v>92778</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5756,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,13 +5780,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574715</v>
+        <v>574695</v>
       </c>
       <c r="R47" t="n">
-        <v>7088499</v>
+        <v>7088500</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5793,9 +5813,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,22 +5840,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338412</v>
+        <v>128338615</v>
       </c>
       <c r="B48" t="n">
-        <v>78840</v>
+        <v>92935</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,21 +5863,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5857,13 +5887,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574702</v>
+        <v>574720</v>
       </c>
       <c r="R48" t="n">
-        <v>7088517</v>
+        <v>7088539</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5890,19 +5920,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,22 +5937,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338040</v>
+        <v>128338482</v>
       </c>
       <c r="B49" t="n">
-        <v>57685</v>
+        <v>92778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,42 +5960,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574732</v>
+        <v>574715</v>
       </c>
       <c r="R49" t="n">
-        <v>7088443</v>
+        <v>7088499</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6002,24 +6017,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338638</v>
+        <v>128338816</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,34 +6281,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574703</v>
+        <v>574676</v>
       </c>
       <c r="R52" t="n">
-        <v>7088547</v>
+        <v>7088536</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6345,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,7 +6355,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,19 +6375,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338816</v>
+        <v>128343377</v>
       </c>
       <c r="B53" t="n">
         <v>57685</v>
@@ -6417,10 +6427,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574676</v>
+        <v>574939</v>
       </c>
       <c r="R53" t="n">
-        <v>7088536</v>
+        <v>7088378</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6452,7 +6462,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,7 +6472,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6494,10 +6504,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128343377</v>
+        <v>128338638</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6505,39 +6515,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574939</v>
+        <v>574703</v>
       </c>
       <c r="R54" t="n">
-        <v>7088378</v>
+        <v>7088547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,12 +6599,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128343651</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R3" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R4" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
         <v>128338768</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128338633</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>128343166</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128344576</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>128343338</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338599</v>
+        <v>128338416</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574696</v>
+        <v>574700</v>
       </c>
       <c r="R11" t="n">
-        <v>7088527</v>
+        <v>7088515</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,19 +1771,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1788,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338416</v>
+        <v>128338599</v>
       </c>
       <c r="B12" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574700</v>
+        <v>574696</v>
       </c>
       <c r="R12" t="n">
-        <v>7088515</v>
+        <v>7088527</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,9 +1868,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,12 +1895,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>128338117</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128338304</v>
+        <v>128343440</v>
       </c>
       <c r="B14" t="n">
-        <v>79702</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2035,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574729</v>
+        <v>574954</v>
       </c>
       <c r="R14" t="n">
-        <v>7088449</v>
+        <v>7088370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R15" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343288</v>
+        <v>128338304</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,39 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574931</v>
+        <v>574729</v>
       </c>
       <c r="R16" t="n">
-        <v>7088374</v>
+        <v>7088449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,12 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
         <v>128343178</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128338659</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128338143</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343500</v>
+        <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>82946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,39 +2717,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574956</v>
+        <v>574994</v>
       </c>
       <c r="R20" t="n">
-        <v>7088362</v>
+        <v>7088388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,12 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,22 +2801,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343223</v>
+        <v>128343500</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574927</v>
+        <v>574956</v>
       </c>
       <c r="R21" t="n">
-        <v>7088381</v>
+        <v>7088362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2940,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343524</v>
+        <v>128343223</v>
       </c>
       <c r="B22" t="n">
-        <v>82942</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,34 +2941,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574994</v>
+        <v>574927</v>
       </c>
       <c r="R22" t="n">
-        <v>7088388</v>
+        <v>7088381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,12 +3035,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
         <v>128338844</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>128338756</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>128338722</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128338797</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,32 +3505,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338557</v>
+        <v>128338166</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>92754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574714</v>
+        <v>574741</v>
       </c>
       <c r="R27" t="n">
-        <v>7088538</v>
+        <v>7088453</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3602,32 +3602,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338166</v>
+        <v>128338557</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>78844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574741</v>
+        <v>574714</v>
       </c>
       <c r="R28" t="n">
-        <v>7088453</v>
+        <v>7088538</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3702,7 +3702,7 @@
         <v>128343150</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>128343147</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>128343435</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338474</v>
+        <v>128338569</v>
       </c>
       <c r="B32" t="n">
-        <v>79702</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,34 +4061,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574723</v>
+        <v>574741</v>
       </c>
       <c r="R32" t="n">
-        <v>7088471</v>
+        <v>7088549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4135,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,22 +4155,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338569</v>
+        <v>128338121</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574741</v>
+        <v>574730</v>
       </c>
       <c r="R33" t="n">
-        <v>7088549</v>
+        <v>7088455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,12 +4252,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338121</v>
+        <v>128338474</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,39 +4295,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574730</v>
+        <v>574723</v>
       </c>
       <c r="R34" t="n">
-        <v>7088455</v>
+        <v>7088471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,7 +4394,7 @@
         <v>128343702</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>128338540</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>128338455</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128343586</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>128338494</v>
       </c>
       <c r="B39" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338168</v>
+        <v>128343543</v>
       </c>
       <c r="B40" t="n">
-        <v>79702</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,34 +4977,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574729</v>
+        <v>574962</v>
       </c>
       <c r="R40" t="n">
-        <v>7088442</v>
+        <v>7088368</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5036,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5051,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,10 +5083,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128338072</v>
+        <v>128338573</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5113,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574723</v>
+        <v>574708</v>
       </c>
       <c r="R41" t="n">
-        <v>7088461</v>
+        <v>7088494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5148,7 +5158,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5158,7 +5168,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5190,10 +5200,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128343543</v>
+        <v>128338072</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,10 +5240,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574962</v>
+        <v>574723</v>
       </c>
       <c r="R42" t="n">
-        <v>7088368</v>
+        <v>7088461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5265,7 +5275,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5285,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128338573</v>
+        <v>128338168</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5318,39 +5328,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574708</v>
+        <v>574729</v>
       </c>
       <c r="R43" t="n">
-        <v>7088494</v>
+        <v>7088442</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5387,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5397,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91713</v>
+        <v>91725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338412</v>
+        <v>128338615</v>
       </c>
       <c r="B45" t="n">
-        <v>78840</v>
+        <v>92947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574702</v>
+        <v>574720</v>
       </c>
       <c r="R45" t="n">
-        <v>7088517</v>
+        <v>7088539</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,12 +5606,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5631,7 +5621,7 @@
         <v>128338040</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5745,10 +5735,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338607</v>
+        <v>128338412</v>
       </c>
       <c r="B47" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5756,21 +5746,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5780,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574695</v>
+        <v>574702</v>
       </c>
       <c r="R47" t="n">
-        <v>7088500</v>
+        <v>7088517</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5815,7 +5805,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5825,7 +5815,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5840,22 +5830,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338615</v>
+        <v>128338482</v>
       </c>
       <c r="B48" t="n">
-        <v>92935</v>
+        <v>92790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5863,21 +5853,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5877,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574720</v>
+        <v>574715</v>
       </c>
       <c r="R48" t="n">
-        <v>7088539</v>
+        <v>7088499</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5949,10 +5939,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338482</v>
+        <v>128338607</v>
       </c>
       <c r="B49" t="n">
-        <v>92778</v>
+        <v>78845</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5960,21 +5950,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5984,13 +5974,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574715</v>
+        <v>574695</v>
       </c>
       <c r="R49" t="n">
-        <v>7088499</v>
+        <v>7088500</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6017,9 +6007,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6049,7 +6049,7 @@
         <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>128338816</v>
       </c>
       <c r="B52" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>128343377</v>
       </c>
       <c r="B53" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>128338638</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -3271,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>78844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,42 +3282,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R25" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,24 +3339,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,19 +3356,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338797</v>
+        <v>128338722</v>
       </c>
       <c r="B26" t="n">
         <v>57689</v>
@@ -3428,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574687</v>
+        <v>574686</v>
       </c>
       <c r="R26" t="n">
-        <v>7088513</v>
+        <v>7088504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3505,48 +3485,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338166</v>
+        <v>128338797</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574741</v>
+        <v>574687</v>
       </c>
       <c r="R27" t="n">
-        <v>7088453</v>
+        <v>7088513</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3573,9 +3558,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,44 +3590,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338557</v>
+        <v>128338166</v>
       </c>
       <c r="B28" t="n">
-        <v>78844</v>
+        <v>92754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574714</v>
+        <v>574741</v>
       </c>
       <c r="R28" t="n">
-        <v>7088538</v>
+        <v>7088453</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>78844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R3" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,7 +907,7 @@
         <v>128338213</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         <v>128344576</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338416</v>
+        <v>128338599</v>
       </c>
       <c r="B11" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574700</v>
+        <v>574696</v>
       </c>
       <c r="R11" t="n">
-        <v>7088515</v>
+        <v>7088527</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,9 +1771,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338599</v>
+        <v>128338117</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574696</v>
+        <v>574773</v>
       </c>
       <c r="R12" t="n">
-        <v>7088527</v>
+        <v>7088446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338117</v>
+        <v>128338416</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1938,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574773</v>
+        <v>574700</v>
       </c>
       <c r="R13" t="n">
-        <v>7088446</v>
+        <v>7088515</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,24 +1995,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343440</v>
+        <v>128338304</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574954</v>
+        <v>574729</v>
       </c>
       <c r="R14" t="n">
-        <v>7088370</v>
+        <v>7088449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,12 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343288</v>
+        <v>128343440</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2181,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574931</v>
+        <v>574954</v>
       </c>
       <c r="R15" t="n">
-        <v>7088374</v>
+        <v>7088370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2258,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338304</v>
+        <v>128343288</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,34 +2259,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574729</v>
+        <v>574931</v>
       </c>
       <c r="R16" t="n">
-        <v>7088449</v>
+        <v>7088374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2333,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2709,7 +2709,7 @@
         <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,39 +3058,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R23" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,12 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,22 +3142,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,34 +3165,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R24" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3239,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3259,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338557</v>
+        <v>128338722</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,37 +3282,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574714</v>
+        <v>574686</v>
       </c>
       <c r="R25" t="n">
-        <v>7088538</v>
+        <v>7088504</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3339,9 +3344,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,19 +3376,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338722</v>
+        <v>128338797</v>
       </c>
       <c r="B26" t="n">
         <v>57689</v>
@@ -3408,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574686</v>
+        <v>574687</v>
       </c>
       <c r="R26" t="n">
-        <v>7088504</v>
+        <v>7088513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3485,53 +3505,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338797</v>
+        <v>128338166</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574687</v>
+        <v>574741</v>
       </c>
       <c r="R27" t="n">
-        <v>7088513</v>
+        <v>7088453</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,24 +3573,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,44 +3590,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338166</v>
+        <v>128338557</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>78846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574741</v>
+        <v>574714</v>
       </c>
       <c r="R28" t="n">
-        <v>7088453</v>
+        <v>7088538</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338569</v>
+        <v>128338474</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,39 +4061,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574741</v>
+        <v>574723</v>
       </c>
       <c r="R32" t="n">
-        <v>7088549</v>
+        <v>7088471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4125,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,12 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4155,19 +4145,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338121</v>
+        <v>128338569</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4207,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574730</v>
+        <v>574741</v>
       </c>
       <c r="R33" t="n">
-        <v>7088455</v>
+        <v>7088549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4242,7 +4232,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,12 +4242,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,22 +4262,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338474</v>
+        <v>128338121</v>
       </c>
       <c r="B34" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4295,34 +4285,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574723</v>
+        <v>574730</v>
       </c>
       <c r="R34" t="n">
-        <v>7088471</v>
+        <v>7088455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4354,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4862,7 +4862,7 @@
         <v>128338494</v>
       </c>
       <c r="B39" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128343543</v>
+        <v>128338168</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,39 +4977,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574962</v>
+        <v>574729</v>
       </c>
       <c r="R40" t="n">
-        <v>7088368</v>
+        <v>7088442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,12 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,7 +5073,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128338573</v>
+        <v>128338072</v>
       </c>
       <c r="B41" t="n">
         <v>57689</v>
@@ -5123,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574708</v>
+        <v>574723</v>
       </c>
       <c r="R41" t="n">
-        <v>7088494</v>
+        <v>7088461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5158,7 +5148,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5168,7 +5158,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5200,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128338072</v>
+        <v>128343543</v>
       </c>
       <c r="B42" t="n">
         <v>57689</v>
@@ -5240,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574723</v>
+        <v>574962</v>
       </c>
       <c r="R42" t="n">
-        <v>7088461</v>
+        <v>7088368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5275,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5285,12 +5275,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5317,10 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128338168</v>
+        <v>128338573</v>
       </c>
       <c r="B43" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5328,34 +5318,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574729</v>
+        <v>574708</v>
       </c>
       <c r="R43" t="n">
-        <v>7088442</v>
+        <v>7088494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5387,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338615</v>
+        <v>128338482</v>
       </c>
       <c r="B45" t="n">
-        <v>92947</v>
+        <v>92792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574720</v>
+        <v>574715</v>
       </c>
       <c r="R45" t="n">
-        <v>7088539</v>
+        <v>7088499</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338040</v>
+        <v>128338607</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,39 +5629,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574732</v>
+        <v>574695</v>
       </c>
       <c r="R46" t="n">
-        <v>7088443</v>
+        <v>7088500</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5693,7 +5688,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5703,12 +5698,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5735,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338412</v>
+        <v>128338615</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>92949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5746,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5770,13 +5760,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574702</v>
+        <v>574720</v>
       </c>
       <c r="R47" t="n">
-        <v>7088517</v>
+        <v>7088539</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5803,19 +5793,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5810,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338482</v>
+        <v>128338412</v>
       </c>
       <c r="B48" t="n">
-        <v>92790</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,21 +5833,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5877,13 +5857,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574715</v>
+        <v>574702</v>
       </c>
       <c r="R48" t="n">
-        <v>7088499</v>
+        <v>7088517</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5910,9 +5890,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,22 +5917,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338607</v>
+        <v>128338040</v>
       </c>
       <c r="B49" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5950,34 +5940,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574695</v>
+        <v>574732</v>
       </c>
       <c r="R49" t="n">
-        <v>7088500</v>
+        <v>7088443</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6004,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6019,7 +6014,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6049,7 +6049,7 @@
         <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,39 +6281,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R52" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,12 +6350,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,19 +6365,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B53" t="n">
         <v>57689</v>
@@ -6427,10 +6417,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R53" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6462,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6472,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6504,10 +6494,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6515,34 +6505,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R54" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6584,7 +6579,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,12 +6599,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R4" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338213</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574711</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128338304</v>
+        <v>128343440</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2035,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574729</v>
+        <v>574954</v>
       </c>
       <c r="R14" t="n">
-        <v>7088449</v>
+        <v>7088370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2171,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R15" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343288</v>
+        <v>128338304</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,39 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574931</v>
+        <v>574729</v>
       </c>
       <c r="R16" t="n">
-        <v>7088374</v>
+        <v>7088449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,12 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343524</v>
+        <v>128343500</v>
       </c>
       <c r="B20" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,34 +2717,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574994</v>
+        <v>574956</v>
       </c>
       <c r="R20" t="n">
-        <v>7088388</v>
+        <v>7088362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2791,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,19 +2811,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343500</v>
+        <v>128343223</v>
       </c>
       <c r="B21" t="n">
         <v>57689</v>
@@ -2853,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574956</v>
+        <v>574927</v>
       </c>
       <c r="R21" t="n">
-        <v>7088362</v>
+        <v>7088381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2930,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343223</v>
+        <v>128343524</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,39 +2951,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574927</v>
+        <v>574994</v>
       </c>
       <c r="R22" t="n">
-        <v>7088381</v>
+        <v>7088388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,12 +3035,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,42 +3282,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R25" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,24 +3339,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,65 +3356,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338797</v>
+        <v>128338166</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574687</v>
+        <v>574741</v>
       </c>
       <c r="R26" t="n">
-        <v>7088513</v>
+        <v>7088453</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,24 +3436,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,60 +3453,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338166</v>
+        <v>128338722</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574741</v>
+        <v>574686</v>
       </c>
       <c r="R27" t="n">
-        <v>7088453</v>
+        <v>7088504</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3573,9 +3538,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,22 +3570,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338557</v>
+        <v>128338797</v>
       </c>
       <c r="B28" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,37 +3593,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574714</v>
+        <v>574687</v>
       </c>
       <c r="R28" t="n">
-        <v>7088538</v>
+        <v>7088513</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,9 +3655,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338474</v>
+        <v>128338569</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,34 +4061,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574723</v>
+        <v>574741</v>
       </c>
       <c r="R32" t="n">
-        <v>7088471</v>
+        <v>7088549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4135,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,19 +4155,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338569</v>
+        <v>128338121</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4197,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574741</v>
+        <v>574730</v>
       </c>
       <c r="R33" t="n">
-        <v>7088549</v>
+        <v>7088455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,12 +4252,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338121</v>
+        <v>128338474</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,39 +4295,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574730</v>
+        <v>574723</v>
       </c>
       <c r="R34" t="n">
-        <v>7088455</v>
+        <v>7088471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5618,10 +5618,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338607</v>
+        <v>128338412</v>
       </c>
       <c r="B46" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,21 +5629,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574695</v>
+        <v>574702</v>
       </c>
       <c r="R46" t="n">
-        <v>7088500</v>
+        <v>7088517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5713,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338615</v>
+        <v>128338607</v>
       </c>
       <c r="B47" t="n">
-        <v>92949</v>
+        <v>78847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,13 +5760,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574720</v>
+        <v>574695</v>
       </c>
       <c r="R47" t="n">
-        <v>7088539</v>
+        <v>7088500</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5793,9 +5793,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,22 +5820,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338412</v>
+        <v>128338615</v>
       </c>
       <c r="B48" t="n">
-        <v>78846</v>
+        <v>92949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,21 +5843,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5857,13 +5867,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574702</v>
+        <v>574720</v>
       </c>
       <c r="R48" t="n">
-        <v>7088517</v>
+        <v>7088539</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5890,19 +5900,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,12 +5917,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128343500</v>
+        <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,39 +2717,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574956</v>
+        <v>574994</v>
       </c>
       <c r="R20" t="n">
-        <v>7088362</v>
+        <v>7088388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,12 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,19 +2801,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343223</v>
+        <v>128343500</v>
       </c>
       <c r="B21" t="n">
         <v>57689</v>
@@ -2863,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574927</v>
+        <v>574956</v>
       </c>
       <c r="R21" t="n">
-        <v>7088381</v>
+        <v>7088362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2940,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343524</v>
+        <v>128343223</v>
       </c>
       <c r="B22" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,34 +2941,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574994</v>
+        <v>574927</v>
       </c>
       <c r="R22" t="n">
-        <v>7088388</v>
+        <v>7088381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3035,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,34 +3058,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R23" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3132,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,22 +3152,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,39 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R24" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,12 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,12 +3259,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338569</v>
+        <v>128338474</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,39 +4061,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574741</v>
+        <v>574723</v>
       </c>
       <c r="R32" t="n">
-        <v>7088549</v>
+        <v>7088471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4125,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,12 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4155,19 +4145,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338121</v>
+        <v>128338569</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -4207,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574730</v>
+        <v>574741</v>
       </c>
       <c r="R33" t="n">
-        <v>7088455</v>
+        <v>7088549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4242,7 +4232,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,12 +4242,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,22 +4262,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338474</v>
+        <v>128338121</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4295,34 +4285,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574723</v>
+        <v>574730</v>
       </c>
       <c r="R34" t="n">
-        <v>7088471</v>
+        <v>7088455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4354,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4359,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338168</v>
+        <v>128338072</v>
       </c>
       <c r="B40" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,34 +4977,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574729</v>
+        <v>574723</v>
       </c>
       <c r="R40" t="n">
-        <v>7088442</v>
+        <v>7088461</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5036,7 +5041,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5051,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5073,7 +5083,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128338072</v>
+        <v>128343543</v>
       </c>
       <c r="B41" t="n">
         <v>57689</v>
@@ -5113,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574723</v>
+        <v>574962</v>
       </c>
       <c r="R41" t="n">
-        <v>7088461</v>
+        <v>7088368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5148,7 +5158,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5158,12 +5168,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5190,7 +5200,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128343543</v>
+        <v>128338573</v>
       </c>
       <c r="B42" t="n">
         <v>57689</v>
@@ -5230,10 +5240,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574962</v>
+        <v>574708</v>
       </c>
       <c r="R42" t="n">
-        <v>7088368</v>
+        <v>7088494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5265,7 +5275,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5285,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128338573</v>
+        <v>128338168</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5318,39 +5328,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574708</v>
+        <v>574729</v>
       </c>
       <c r="R43" t="n">
-        <v>7088494</v>
+        <v>7088442</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5387,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5397,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R3" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R4" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128338633</v>
+        <v>128343166</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574688</v>
+        <v>574867</v>
       </c>
       <c r="R7" t="n">
-        <v>7088504</v>
+        <v>7088386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128343166</v>
+        <v>128338633</v>
       </c>
       <c r="B8" t="n">
         <v>57689</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574867</v>
+        <v>574688</v>
       </c>
       <c r="R8" t="n">
-        <v>7088386</v>
+        <v>7088504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338599</v>
+        <v>128338117</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574696</v>
+        <v>574773</v>
       </c>
       <c r="R11" t="n">
-        <v>7088527</v>
+        <v>7088446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338117</v>
+        <v>128338416</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,42 +1831,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574773</v>
+        <v>574700</v>
       </c>
       <c r="R12" t="n">
-        <v>7088446</v>
+        <v>7088515</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,24 +1888,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338416</v>
+        <v>128338599</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,13 +1952,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574700</v>
+        <v>574696</v>
       </c>
       <c r="R13" t="n">
-        <v>7088515</v>
+        <v>7088527</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,9 +1985,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343440</v>
+        <v>128338304</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574954</v>
+        <v>574729</v>
       </c>
       <c r="R14" t="n">
-        <v>7088370</v>
+        <v>7088449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,12 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338304</v>
+        <v>128343440</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,34 +2259,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574729</v>
+        <v>574954</v>
       </c>
       <c r="R16" t="n">
-        <v>7088449</v>
+        <v>7088370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2333,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128338844</v>
+        <v>128338756</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,39 +3058,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574674</v>
+        <v>574654</v>
       </c>
       <c r="R23" t="n">
-        <v>7088545</v>
+        <v>7088561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,12 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,22 +3142,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338756</v>
+        <v>128338844</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,34 +3165,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574654</v>
+        <v>574674</v>
       </c>
       <c r="R24" t="n">
-        <v>7088561</v>
+        <v>7088545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3239,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,44 +3259,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338557</v>
+        <v>128338166</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574714</v>
+        <v>574741</v>
       </c>
       <c r="R25" t="n">
-        <v>7088538</v>
+        <v>7088453</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3368,32 +3368,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338166</v>
+        <v>128338557</v>
       </c>
       <c r="B26" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574741</v>
+        <v>574714</v>
       </c>
       <c r="R26" t="n">
-        <v>7088453</v>
+        <v>7088538</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B35" t="n">
         <v>57689</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R35" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B36" t="n">
         <v>57689</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R36" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128338072</v>
+        <v>128338168</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,39 +4977,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574723</v>
+        <v>574729</v>
       </c>
       <c r="R40" t="n">
-        <v>7088461</v>
+        <v>7088442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,12 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,7 +5073,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128343543</v>
+        <v>128338072</v>
       </c>
       <c r="B41" t="n">
         <v>57689</v>
@@ -5123,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574962</v>
+        <v>574723</v>
       </c>
       <c r="R41" t="n">
-        <v>7088368</v>
+        <v>7088461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5158,7 +5148,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5168,12 +5158,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5317,10 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128338168</v>
+        <v>128343543</v>
       </c>
       <c r="B43" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5328,34 +5318,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574729</v>
+        <v>574962</v>
       </c>
       <c r="R43" t="n">
-        <v>7088442</v>
+        <v>7088368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5387,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338482</v>
+        <v>128338040</v>
       </c>
       <c r="B45" t="n">
-        <v>92792</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,37 +5532,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574715</v>
+        <v>574732</v>
       </c>
       <c r="R45" t="n">
-        <v>7088499</v>
+        <v>7088443</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,9 +5594,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5606,22 +5626,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338412</v>
+        <v>128338482</v>
       </c>
       <c r="B46" t="n">
-        <v>78846</v>
+        <v>92793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,21 +5649,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,13 +5673,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574702</v>
+        <v>574715</v>
       </c>
       <c r="R46" t="n">
-        <v>7088517</v>
+        <v>7088499</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5686,19 +5706,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5723,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338607</v>
+        <v>128338412</v>
       </c>
       <c r="B47" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5746,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574695</v>
+        <v>574702</v>
       </c>
       <c r="R47" t="n">
-        <v>7088500</v>
+        <v>7088517</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,7 +5805,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5805,7 +5815,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5820,12 +5830,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5835,7 +5845,7 @@
         <v>128338615</v>
       </c>
       <c r="B48" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5929,10 +5939,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338040</v>
+        <v>128338607</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,39 +5950,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574732</v>
+        <v>574695</v>
       </c>
       <c r="R49" t="n">
-        <v>7088443</v>
+        <v>7088500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6004,7 +6009,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6014,12 +6019,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,39 +6057,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R50" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6121,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6131,12 +6126,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,10 +6153,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,34 +6164,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R51" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6233,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6243,7 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338213</v>
+        <v>128338613</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574711</v>
+        <v>574703</v>
       </c>
       <c r="R3" t="n">
-        <v>7088512</v>
+        <v>7088527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R4" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338213</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574711</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088512</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343288</v>
+        <v>128343440</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574931</v>
+        <v>574954</v>
       </c>
       <c r="R15" t="n">
-        <v>7088374</v>
+        <v>7088370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B16" t="n">
         <v>57689</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R16" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338040</v>
+        <v>128338607</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,39 +5532,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574732</v>
+        <v>574695</v>
       </c>
       <c r="R45" t="n">
-        <v>7088443</v>
+        <v>7088500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,7 +5591,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5606,12 +5601,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5939,10 +5929,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338607</v>
+        <v>128338040</v>
       </c>
       <c r="B49" t="n">
-        <v>78847</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5950,34 +5940,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574695</v>
+        <v>574732</v>
       </c>
       <c r="R49" t="n">
-        <v>7088500</v>
+        <v>7088443</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +6004,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6019,7 +6014,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128338638</v>
+        <v>128343377</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,34 +6281,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574703</v>
+        <v>574939</v>
       </c>
       <c r="R52" t="n">
-        <v>7088547</v>
+        <v>7088378</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6345,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,7 +6355,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6365,22 +6375,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338816</v>
+        <v>128338638</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6388,39 +6398,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574676</v>
+        <v>574703</v>
       </c>
       <c r="R53" t="n">
-        <v>7088536</v>
+        <v>7088547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6452,7 +6457,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,12 +6467,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,19 +6482,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128343377</v>
+        <v>128338816</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574939</v>
+        <v>574676</v>
       </c>
       <c r="R54" t="n">
-        <v>7088378</v>
+        <v>7088536</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128343651</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128338613</v>
+        <v>128338213</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574703</v>
+        <v>574711</v>
       </c>
       <c r="R3" t="n">
-        <v>7088527</v>
+        <v>7088512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R4" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128338213</v>
+        <v>128337994</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574711</v>
+        <v>574735</v>
       </c>
       <c r="R5" t="n">
-        <v>7088512</v>
+        <v>7088435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
         <v>128338768</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128343166</v>
+        <v>128338633</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574867</v>
+        <v>574688</v>
       </c>
       <c r="R7" t="n">
-        <v>7088386</v>
+        <v>7088504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128338633</v>
+        <v>128343166</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574688</v>
+        <v>574867</v>
       </c>
       <c r="R8" t="n">
-        <v>7088504</v>
+        <v>7088386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         <v>128344576</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>128343338</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338117</v>
+        <v>128338599</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574773</v>
+        <v>574696</v>
       </c>
       <c r="R11" t="n">
-        <v>7088446</v>
+        <v>7088527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338416</v>
+        <v>128338117</v>
       </c>
       <c r="B12" t="n">
-        <v>78847</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,37 +1821,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574700</v>
+        <v>574773</v>
       </c>
       <c r="R12" t="n">
-        <v>7088515</v>
+        <v>7088446</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,9 +1883,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1915,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338599</v>
+        <v>128338416</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,13 +1962,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574696</v>
+        <v>574700</v>
       </c>
       <c r="R13" t="n">
-        <v>7088527</v>
+        <v>7088515</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,19 +1995,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128338304</v>
+        <v>128343440</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2035,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574729</v>
+        <v>574954</v>
       </c>
       <c r="R14" t="n">
-        <v>7088449</v>
+        <v>7088370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343440</v>
+        <v>128343288</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574954</v>
+        <v>574931</v>
       </c>
       <c r="R15" t="n">
-        <v>7088370</v>
+        <v>7088374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2248,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128343288</v>
+        <v>128338304</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,39 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574931</v>
+        <v>574729</v>
       </c>
       <c r="R16" t="n">
-        <v>7088374</v>
+        <v>7088449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,12 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
         <v>128343178</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128338659</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128338143</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128343524</v>
       </c>
       <c r="B20" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>128343500</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>128343223</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>128338756</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128338844</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,48 +3271,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338166</v>
+        <v>128338722</v>
       </c>
       <c r="B25" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574741</v>
+        <v>574686</v>
       </c>
       <c r="R25" t="n">
-        <v>7088453</v>
+        <v>7088504</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3339,9 +3344,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,22 +3376,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338557</v>
+        <v>128338797</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,37 +3399,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574714</v>
+        <v>574687</v>
       </c>
       <c r="R26" t="n">
-        <v>7088538</v>
+        <v>7088513</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,9 +3461,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,22 +3493,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>78873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,42 +3516,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R27" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3538,24 +3573,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3570,65 +3590,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128338797</v>
+        <v>128338166</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574687</v>
+        <v>574741</v>
       </c>
       <c r="R28" t="n">
-        <v>7088513</v>
+        <v>7088453</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,24 +3670,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
         <v>128343150</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>128343147</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>128343435</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>128338474</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>128338569</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128338121</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128338540</v>
+        <v>128343702</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574700</v>
+        <v>575023</v>
       </c>
       <c r="R35" t="n">
-        <v>7088489</v>
+        <v>7088330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128343702</v>
+        <v>128338540</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575023</v>
+        <v>574700</v>
       </c>
       <c r="R36" t="n">
-        <v>7088330</v>
+        <v>7088489</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,7 +4628,7 @@
         <v>128338455</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>128343586</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>128338494</v>
       </c>
       <c r="B39" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>128338168</v>
       </c>
       <c r="B40" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>128338072</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128338573</v>
+        <v>128343543</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574708</v>
+        <v>574962</v>
       </c>
       <c r="R42" t="n">
-        <v>7088494</v>
+        <v>7088368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128343543</v>
+        <v>128338573</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574962</v>
+        <v>574708</v>
       </c>
       <c r="R43" t="n">
-        <v>7088368</v>
+        <v>7088494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,7 +5427,7 @@
         <v>128338600</v>
       </c>
       <c r="B44" t="n">
-        <v>91728</v>
+        <v>91755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128338607</v>
+        <v>128338615</v>
       </c>
       <c r="B45" t="n">
-        <v>78847</v>
+        <v>92977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5556,13 +5556,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574695</v>
+        <v>574720</v>
       </c>
       <c r="R45" t="n">
-        <v>7088500</v>
+        <v>7088539</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,22 +5606,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338482</v>
+        <v>128338040</v>
       </c>
       <c r="B46" t="n">
-        <v>92793</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,37 +5629,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574715</v>
+        <v>574732</v>
       </c>
       <c r="R46" t="n">
-        <v>7088499</v>
+        <v>7088443</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5696,9 +5691,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,22 +5723,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338412</v>
+        <v>128338607</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5736,21 +5746,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,10 +5770,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574702</v>
+        <v>574695</v>
       </c>
       <c r="R47" t="n">
-        <v>7088517</v>
+        <v>7088500</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,7 +5805,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5805,7 +5815,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5820,22 +5830,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338615</v>
+        <v>128338412</v>
       </c>
       <c r="B48" t="n">
-        <v>92950</v>
+        <v>78873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5843,21 +5853,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5867,13 +5877,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574720</v>
+        <v>574702</v>
       </c>
       <c r="R48" t="n">
-        <v>7088539</v>
+        <v>7088517</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5900,9 +5910,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,22 +5937,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338040</v>
+        <v>128338482</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>92820</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,42 +5960,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574732</v>
+        <v>574715</v>
       </c>
       <c r="R49" t="n">
-        <v>7088443</v>
+        <v>7088499</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6002,24 +6017,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,12 +6034,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6049,7 +6049,7 @@
         <v>128338537</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>128338052</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128343377</v>
+        <v>128338638</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,39 +6281,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574939</v>
+        <v>574703</v>
       </c>
       <c r="R52" t="n">
-        <v>7088378</v>
+        <v>7088547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6355,12 +6350,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,22 +6365,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128338638</v>
+        <v>128338816</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6398,34 +6388,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574703</v>
+        <v>574676</v>
       </c>
       <c r="R53" t="n">
-        <v>7088547</v>
+        <v>7088536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6467,7 +6462,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,22 +6482,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128338816</v>
+        <v>128343377</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574676</v>
+        <v>574939</v>
       </c>
       <c r="R54" t="n">
-        <v>7088536</v>
+        <v>7088378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/artfynd/A 22960-2022 artfynd.xlsx
+++ b/artfynd/A 22960-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128338613</v>
+        <v>128337994</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574703</v>
+        <v>574735</v>
       </c>
       <c r="R4" t="n">
-        <v>7088527</v>
+        <v>7088435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128337994</v>
+        <v>128338613</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574735</v>
+        <v>574703</v>
       </c>
       <c r="R5" t="n">
-        <v>7088435</v>
+        <v>7088527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128338768</v>
+        <v>128343166</v>
       </c>
       <c r="B6" t="n">
         <v>57716</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574690</v>
+        <v>574867</v>
       </c>
       <c r="R6" t="n">
-        <v>7088519</v>
+        <v>7088386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,19 +1233,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128338633</v>
+        <v>128338768</v>
       </c>
       <c r="B7" t="n">
         <v>57716</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574688</v>
+        <v>574690</v>
       </c>
       <c r="R7" t="n">
-        <v>7088504</v>
+        <v>7088519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128343166</v>
+        <v>128338633</v>
       </c>
       <c r="B8" t="n">
         <v>57716</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574867</v>
+        <v>574688</v>
       </c>
       <c r="R8" t="n">
-        <v>7088386</v>
+        <v>7088504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1467,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128338599</v>
+        <v>128338416</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574696</v>
+        <v>574700</v>
       </c>
       <c r="R11" t="n">
-        <v>7088527</v>
+        <v>7088515</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,19 +1771,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,22 +1788,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128338117</v>
+        <v>128338599</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574773</v>
+        <v>574696</v>
       </c>
       <c r="R12" t="n">
-        <v>7088446</v>
+        <v>7088527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128338416</v>
+        <v>128338117</v>
       </c>
       <c r="B13" t="n">
-        <v>78874</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,37 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574700</v>
+        <v>574773</v>
       </c>
       <c r="R13" t="n">
-        <v>7088515</v>
+        <v>7088446</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,9 +1980,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128343440</v>
+        <v>128338304</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>79735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574954</v>
+        <v>574729</v>
       </c>
       <c r="R14" t="n">
-        <v>7088370</v>
+        <v>7088449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,12 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128343288</v>
+        <v>128343440</v>
       </c>
       <c r="B15" t="n">
         <v>57716</v>
@@ -2181,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574931</v>
+        <v>574954</v>
       </c>
       <c r="R15" t="n">
-        <v>7088374</v>
+        <v>7088370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2258,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128338304</v>
+        <v>128343288</v>
       </c>
       <c r="B16" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,34 +2259,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574729</v>
+        <v>574931</v>
       </c>
       <c r="R16" t="n">
-        <v>7088449</v>
+        <v>7088374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2333,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128343178</v>
+        <v>128338143</v>
       </c>
       <c r="B17" t="n">
         <v>57716</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574894</v>
+        <v>574745</v>
       </c>
       <c r="R17" t="n">
-        <v>7088378</v>
+        <v>7088485</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,24 +2438,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,19 +2460,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128338659</v>
+        <v>128343178</v>
       </c>
       <c r="B18" t="n">
         <v>57716</v>
@@ -2522,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574695</v>
+        <v>574894</v>
       </c>
       <c r="R18" t="n">
-        <v>7088514</v>
+        <v>7088378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2557,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,12 +2557,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,7 +2589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128338143</v>
+        <v>128338659</v>
       </c>
       <c r="B19" t="n">
         <v>57716</v>
@@ -2639,13 +2629,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574745</v>
+        <v>574695</v>
       </c>
       <c r="R19" t="n">
-        <v>7088485</v>
+        <v>7088514</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2672,14 +2662,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,12 +2694,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128343500</v>
+        <v>128343223</v>
       </c>
       <c r="B21" t="n">
         <v>57716</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574956</v>
+        <v>574927</v>
       </c>
       <c r="R21" t="n">
-        <v>7088362</v>
+        <v>7088381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128343223</v>
+        <v>128343500</v>
       </c>
       <c r="B22" t="n">
         <v>57716</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574927</v>
+        <v>574956</v>
       </c>
       <c r="R22" t="n">
-        <v>7088381</v>
+        <v>7088362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338722</v>
+        <v>128338557</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,42 +3282,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574686</v>
+        <v>574714</v>
       </c>
       <c r="R25" t="n">
-        <v>7088504</v>
+        <v>7088538</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,24 +3339,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,19 +3356,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128338797</v>
+        <v>128338722</v>
       </c>
       <c r="B26" t="n">
         <v>57716</v>
@@ -3428,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574687</v>
+        <v>574686</v>
       </c>
       <c r="R26" t="n">
-        <v>7088513</v>
+        <v>7088504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3505,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128338557</v>
+        <v>128338797</v>
       </c>
       <c r="B27" t="n">
-        <v>78873</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,37 +3496,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574714</v>
+        <v>574687</v>
       </c>
       <c r="R27" t="n">
-        <v>7088538</v>
+        <v>7088513</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3573,9 +3558,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,12 +3590,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128338474</v>
+        <v>128338569</v>
       </c>
       <c r="B32" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,34 +4061,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574723</v>
+        <v>574741</v>
       </c>
       <c r="R32" t="n">
-        <v>7088471</v>
+        <v>7088549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4135,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,19 +4155,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128338569</v>
+        <v>128338121</v>
       </c>
       <c r="B33" t="n">
         <v>57716</v>
@@ -4197,10 +4207,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574741</v>
+        <v>574730</v>
       </c>
       <c r="R33" t="n">
-        <v>7088549</v>
+        <v>7088455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,12 +4252,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128338121</v>
+        <v>128338474</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>79735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,39 +4295,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574730</v>
+        <v>574723</v>
       </c>
       <c r="R34" t="n">
-        <v>7088455</v>
+        <v>7088471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4359,12 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5618,10 +5618,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128338040</v>
+        <v>128338412</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5629,39 +5629,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574732</v>
+        <v>574702</v>
       </c>
       <c r="R46" t="n">
-        <v>7088443</v>
+        <v>7088517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5693,7 +5688,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5703,12 +5698,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5723,22 +5713,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128338607</v>
+        <v>128338482</v>
       </c>
       <c r="B47" t="n">
-        <v>78874</v>
+        <v>92820</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5746,21 +5736,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5770,13 +5760,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574695</v>
+        <v>574715</v>
       </c>
       <c r="R47" t="n">
-        <v>7088500</v>
+        <v>7088499</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5803,19 +5793,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,22 +5810,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128338412</v>
+        <v>128338040</v>
       </c>
       <c r="B48" t="n">
-        <v>78873</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,34 +5833,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574702</v>
+        <v>574732</v>
       </c>
       <c r="R48" t="n">
-        <v>7088517</v>
+        <v>7088443</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5912,7 +5897,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5922,7 +5907,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,22 +5927,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128338482</v>
+        <v>128338607</v>
       </c>
       <c r="B49" t="n">
-        <v>92820</v>
+        <v>78874</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5960,21 +5950,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5984,13 +5974,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574715</v>
+        <v>574695</v>
       </c>
       <c r="R49" t="n">
-        <v>7088499</v>
+        <v>7088500</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6017,9 +6007,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,22 +6034,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128338537</v>
+        <v>128338052</v>
       </c>
       <c r="B50" t="n">
-        <v>78873</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6057,34 +6057,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574719</v>
+        <v>574757</v>
       </c>
       <c r="R50" t="n">
-        <v>7088533</v>
+        <v>7088425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6121,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,7 +6131,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6153,10 +6163,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128338052</v>
+        <v>128338537</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>78873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,39 +6174,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster-Långvattnet, Väster-Långvattnet, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574757</v>
+        <v>574719</v>
       </c>
       <c r="R51" t="n">
-        <v>7088425</v>
+        <v>7088533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6233,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6243,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
